--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BFD701-74F7-41F4-8BCF-5D95A8C53E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99ED6D1-6EC0-4238-B10A-E8A6F556A174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="1650" windowWidth="23505" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28245" yWindow="945" windowWidth="28215" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
-  <si>
-    <t>우리가 바빠지면서 아무래도 서로에게 상대적으로 뜸해져서 그런거 아니었을까? &lt;np&gt;사람들이 다들 말하는 권태기처럼 찾아온 시간이고, 우리가 극복하면 더 가깝고 좋은 사이가 되지 않을까 싶어.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
   <si>
     <t>너도 지금은 집중해야하는 일이 있고, 서로가 서로를 잊기에 충분한 시간일거라고 생각했어.</t>
   </si>
   <si>
-    <t>아니야.. 나는 여전히 내가 그리는 미래에는 너가 그려지지 않아..&lt;np&gt;그리고 무엇보다 내가 너를 더이상 좋아하지 않는다는 감정이 들었어. &lt;np&gt;얼마전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.&lt;np&gt; 근데 오늘 느낀 감정은 그냥 다른 친구들이 한 행동처럼 '음 그럴 수 있지,' 라고 느꼈어.. &lt;np&gt;이런 감정에서 나는 너에 대한 애정이 식었고, 2달전부터 해온 생각들이 틀리지 않았음을 직감했어.</t>
-  </si>
-  <si>
     <t>SelectionNameList</t>
   </si>
   <si>
@@ -67,31 +61,15 @@
     <t>character_Player_01</t>
   </si>
   <si>
-    <t>많이 힘들겠지만 노력해야지.. 아니? 해야만해&lt;np&gt; 우리.. 내일 서로의 일정이 있고, 달려가야 할 길이 있잖아! 일찍 자자 ..&lt;np&gt;안녕 이제 더이상 말하지 않아줬으면 좋겠어. 흔들리고 싶지않아. 이만 끊을게</t>
-  </si>
-  <si>
     <t>character_Minhyeong_01</t>
   </si>
   <si>
-    <t>아니? 내 생각은 달라. &lt;np&gt;우리가 지금 끊어내지 못하고 계속 사귄다면 결국 결혼이라는 문제와 맞닥뜨리게 될텐데 너와 나는 결혼에 대한 로망도, 가치관도 다르잖아.. &lt;np&gt;내가 그린 미래에는 너가 없다고 말했잖아.. 나는 너와 결혼 할 수 없어. &lt;np&gt;그렇기 때문에 극복할 가치가 없고, 지금은 내가 하는 일에 집중하고 싶어. 미안해..</t>
-  </si>
-  <si>
     <t>혹시 나의 모습에서 실망하고, 내가 싫어진 계기가 있는거야?</t>
   </si>
   <si>
-    <t>우리가 바쁘다는 것을 기회로 삼을 만큼 헤어져야만 하는 사이일까..? &lt;np&gt;물론 헤어지기로 했던 사이인건 맞지. 하지만 그 생각을 변화 시키기 위해서 나는 최선을 다했고, 이번에 느낀 감정 또한 나는 극복하고, 우리의 관계가 더 성장하며, 성숙해지는 과정이 아닐까?</t>
-  </si>
-  <si>
-    <t>정말 나 매번 너를 잡았는데,, 그건 너가 나를 좋아한다는 마음이 있을때 할 수 있는 일이었어... &lt;np&gt;하지만 지금처럼 너가 나를 안좋아한다는데 차마 너를 잡을 수가 없네..&lt;np&gt;내가 없는 일상,내가 없는 너의 옆자리, 너는 괜찮아?? 견딜 수 있어??</t>
-  </si>
-  <si>
     <t>너가 잘못한거 없고, 단지 사랑이 식은거 뿐이야.</t>
   </si>
   <si>
-    <t>우리는 4년이라는 긴 시간동안 많이 싸우기도 했고, 헤어 질 뻔한적도 있었지만 흔들리지 않고 잘 만나 행복한 시간이었어.&lt;np&gt; 그렇지만 우리는 이제 여기까지 해야할거 해야 할거 같아...&lt;np&gt;갑자기 든 생각도 아니니고, 2달 전부터 천천히 정리하면서 고민하고 말하는거야.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>요즘 우리는 서로 매우 바쁜 삶을 살고 있고, 전에 말했던 헤어짐의 타이밍이지 않을까 싶어. 가장 힘들지 않게 이별 할 수 있는 기회라고 생각했어.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -100,66 +78,243 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>mindDialogue_Opening_1_1_107</t>
-  </si>
-  <si>
     <t>NextDialogueId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>normalDialogue_Opening_1_1_104</t>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_105</t>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_106</t>
-  </si>
-  <si>
     <t>normalDialogue_Opening_1_1_110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇지만 우리는 이제 여기까지 해야할거 해야 할거 같아…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 든 생각도 아니니고, 2달 전부터 천천히 정리하면서 고민하고 말하는거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 4년이라는 긴 시간동안 많이 싸우기도 했고, 헤어 질 뻔한적도 있었지만 흔들리지 않고 잘 만나 행복한 시간이었어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Minhyeong_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>normalDialogue_Opening_1_1_111</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_112</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_112</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>normalDialogue_Opening_1_1_113</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>normalDialogue_Opening_1_1_114</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_115</t>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_116</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>normalDialogue_Opening_1_1_117</t>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_118</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_119</t>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_120</t>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_121</t>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_122</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Player_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>물론 헤어지기로 했던 사이인건 맞지. 하지만 그 생각을 변화 시키기 위해서 나는 최선을 다했고, 이번에 느낀 감정 또한 나는 극복하고, 우리의 관계가 더 성장하며, 성숙해지는 과정이 아닐까?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">우리가 바쁘다는 것을 기회로 삼을 만큼 헤어져야만 하는 사이일까..? </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그리고 무엇보다 내가 너를 더이상 좋아하지 않는다는 감정이 들었어. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼마전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니야.. 나는 여전히 내가 그리는 미래에는 너가 그려지지 않아..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런 감정에서 나는 너에 대한 애정이 식었고, 2달전부터 해온 생각들이 틀리지 않았음을 직감했어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">근데 오늘 느낀 감정은 그냥 다른 친구들이 한 행동처럼 '음 그럴 수 있지,' 라고 느꼈어.. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_118</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_129</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_130</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_131</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_132</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_133</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_134</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_135</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_136</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_138</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사람들이 다들 말하는 권태기처럼 찾아온 시간이고, 우리가 극복하면 더 가깝고 좋은 사이가 되지 않을까 싶어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">우리가 바빠지면서 아무래도 서로에게 상대적으로 뜸해져서 그런거 아니었을까? </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_139</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_140</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_141</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_142</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리가 지금 끊어내지 못하고 계속 사귄다면 결국 결혼이라는 문제와 맞닥뜨리게 될텐데 너와 나는 결혼에 대한 로망도, 가치관도 다르잖아..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 그린 미래에는 너가 없다고 말했잖아.. 나는 너와 결혼 할 수 없어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇기 때문에 극복할 가치가 없고, 지금은 내가 하는 일에 집중하고 싶어. 미안해..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_143</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아니? 내 생각은 달라. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_144</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_147</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_148</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_149</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_150</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_154</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 지금처럼 너가 나를 안좋아한다는데 차마 너를 잡을 수가 없네.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 없는 일상,내가 없는 너의 옆자리, 너는 괜찮아?? 견딜 수 있어??</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">정말 나 매번 너를 잡았는데,, 그건 너가 나를 좋아한다는 마음이 있을때 할 수 있는 일이었어... </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_155</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_156</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_157</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">많이 힘들겠지만 노력해야지.. 아니? 해야만해&lt;np&gt; </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리.. 내일 서로의 일정이 있고, 달려가야 할 길이 있잖아! 일찍 자자 ..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕 이제 더이상 말하지 않아줬으면 좋겠어. 흔들리고 싶지않아. 이만 끊을게</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_158</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_159</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_160</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -181,6 +336,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -253,7 +415,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -273,6 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -491,19 +654,20 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H1013"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
-    <col min="4" max="6" width="77.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="99.28515625" customWidth="1"/>
+    <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="77.140625" customWidth="1"/>
     <col min="7" max="8" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -515,120 +679,116 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+        <v>25</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+        <v>26</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -637,88 +797,88 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="D11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>14</v>
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -727,271 +887,508 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+      <c r="D24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+      <c r="A25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="A26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="A27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="A28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="A29" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="A30" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+    </row>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1944,6 +2341,19 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99ED6D1-6EC0-4238-B10A-E8A6F556A174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5533D1-38AC-4ED3-B0F6-4EA7BF27F815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28245" yWindow="945" windowWidth="28215" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
   <si>
     <t>너도 지금은 집중해야하는 일이 있고, 서로가 서로를 잊기에 충분한 시간일거라고 생각했어.</t>
   </si>
@@ -28,285 +28,294 @@
     <t>SelectionNameList</t>
   </si>
   <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>SelectionDialogueIdList</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>VoicePath</t>
+  </si>
+  <si>
+    <t>TexturePath</t>
+  </si>
+  <si>
+    <t>고유 ID</t>
+  </si>
+  <si>
+    <t>(name)</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>character_Player_01</t>
+  </si>
+  <si>
+    <t>character_Minhyeong_01</t>
+  </si>
+  <si>
+    <t>혹시 나의 모습에서 실망하고, 내가 싫어진 계기가 있는거야?</t>
+  </si>
+  <si>
+    <t>너가 잘못한거 없고, 단지 사랑이 식은거 뿐이야.</t>
+  </si>
+  <si>
+    <t>요즘 우리는 서로 매우 바쁜 삶을 살고 있고, 전에 말했던 헤어짐의 타이밍이지 않을까 싶어. 가장 힘들지 않게 이별 할 수 있는 기회라고 생각했어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>......</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextDialogueId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_110</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇지만 우리는 이제 여기까지 해야할거 해야 할거 같아…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 든 생각도 아니니고, 2달 전부터 천천히 정리하면서 고민하고 말하는거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 4년이라는 긴 시간동안 많이 싸우기도 했고, 헤어 질 뻔한적도 있었지만 흔들리지 않고 잘 만나 행복한 시간이었어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Minhyeong_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_111</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_112</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_113</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_114</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_117</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Player_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>물론 헤어지기로 했던 사이인건 맞지. 하지만 그 생각을 변화 시키기 위해서 나는 최선을 다했고, 이번에 느낀 감정 또한 나는 극복하고, 우리의 관계가 더 성장하며, 성숙해지는 과정이 아닐까?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">우리가 바쁘다는 것을 기회로 삼을 만큼 헤어져야만 하는 사이일까..? </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그리고 무엇보다 내가 너를 더이상 좋아하지 않는다는 감정이 들었어. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼마전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니야.. 나는 여전히 내가 그리는 미래에는 너가 그려지지 않아..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런 감정에서 나는 너에 대한 애정이 식었고, 2달전부터 해온 생각들이 틀리지 않았음을 직감했어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">근데 오늘 느낀 감정은 그냥 다른 친구들이 한 행동처럼 '음 그럴 수 있지,' 라고 느꼈어.. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_118</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_129</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_130</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_131</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_132</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_133</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_134</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_135</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_136</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_138</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사람들이 다들 말하는 권태기처럼 찾아온 시간이고, 우리가 극복하면 더 가깝고 좋은 사이가 되지 않을까 싶어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">우리가 바빠지면서 아무래도 서로에게 상대적으로 뜸해져서 그런거 아니었을까? </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_139</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_140</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_141</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_142</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리가 지금 끊어내지 못하고 계속 사귄다면 결국 결혼이라는 문제와 맞닥뜨리게 될텐데 너와 나는 결혼에 대한 로망도, 가치관도 다르잖아..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 그린 미래에는 너가 없다고 말했잖아.. 나는 너와 결혼 할 수 없어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇기 때문에 극복할 가치가 없고, 지금은 내가 하는 일에 집중하고 싶어. 미안해..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_143</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아니? 내 생각은 달라. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_144</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_147</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_148</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_149</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_150</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_154</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 지금처럼 너가 나를 안좋아한다는데 차마 너를 잡을 수가 없네.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 없는 일상,내가 없는 너의 옆자리, 너는 괜찮아?? 견딜 수 있어??</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">정말 나 매번 너를 잡았는데,, 그건 너가 나를 좋아한다는 마음이 있을때 할 수 있는 일이었어... </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_155</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_156</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_157</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">많이 힘들겠지만 노력해야지.. 아니? 해야만해&lt;np&gt; </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리.. 내일 서로의 일정이 있고, 달려가야 할 길이 있잖아! 일찍 자자 ..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕 이제 더이상 말하지 않아줬으면 좋겠어. 흔들리고 싶지않아. 이만 끊을게</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_158</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_159</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_160</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜 그렇게 생각했는데?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_115</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>CharacterDataId</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>string[]</t>
-  </si>
-  <si>
-    <t>VoicePath</t>
-  </si>
-  <si>
-    <t>TexturePath</t>
-  </si>
-  <si>
-    <t>고유 ID</t>
-  </si>
-  <si>
-    <t>(name)</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>character_Player_01</t>
-  </si>
-  <si>
-    <t>character_Minhyeong_01</t>
-  </si>
-  <si>
-    <t>혹시 나의 모습에서 실망하고, 내가 싫어진 계기가 있는거야?</t>
-  </si>
-  <si>
-    <t>너가 잘못한거 없고, 단지 사랑이 식은거 뿐이야.</t>
-  </si>
-  <si>
-    <t>요즘 우리는 서로 매우 바쁜 삶을 살고 있고, 전에 말했던 헤어짐의 타이밍이지 않을까 싶어. 가장 힘들지 않게 이별 할 수 있는 기회라고 생각했어.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>......</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NextDialogueId</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_110</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇지만 우리는 이제 여기까지 해야할거 해야 할거 같아…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>갑자기 든 생각도 아니니고, 2달 전부터 천천히 정리하면서 고민하고 말하는거야.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리는 4년이라는 긴 시간동안 많이 싸우기도 했고, 헤어 질 뻔한적도 있었지만 흔들리지 않고 잘 만나 행복한 시간이었어.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Minhyeong_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_111</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_112</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_113</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_114</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_117</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Player_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>물론 헤어지기로 했던 사이인건 맞지. 하지만 그 생각을 변화 시키기 위해서 나는 최선을 다했고, 이번에 느낀 감정 또한 나는 극복하고, 우리의 관계가 더 성장하며, 성숙해지는 과정이 아닐까?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">우리가 바쁘다는 것을 기회로 삼을 만큼 헤어져야만 하는 사이일까..? </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">그리고 무엇보다 내가 너를 더이상 좋아하지 않는다는 감정이 들었어. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>얼마전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아니야.. 나는 여전히 내가 그리는 미래에는 너가 그려지지 않아..</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이런 감정에서 나는 너에 대한 애정이 식었고, 2달전부터 해온 생각들이 틀리지 않았음을 직감했어.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">근데 오늘 느낀 감정은 그냥 다른 친구들이 한 행동처럼 '음 그럴 수 있지,' 라고 느꼈어.. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_118</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_129</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_130</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_131</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_132</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_133</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_134</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_135</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_136</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_138</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사람들이 다들 말하는 권태기처럼 찾아온 시간이고, 우리가 극복하면 더 가깝고 좋은 사이가 되지 않을까 싶어.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">우리가 바빠지면서 아무래도 서로에게 상대적으로 뜸해져서 그런거 아니었을까? </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_139</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_140</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_141</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_142</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리가 지금 끊어내지 못하고 계속 사귄다면 결국 결혼이라는 문제와 맞닥뜨리게 될텐데 너와 나는 결혼에 대한 로망도, 가치관도 다르잖아..</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>내가 그린 미래에는 너가 없다고 말했잖아.. 나는 너와 결혼 할 수 없어.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇기 때문에 극복할 가치가 없고, 지금은 내가 하는 일에 집중하고 싶어. 미안해..</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_143</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">아니? 내 생각은 달라. </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_144</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_147</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_148</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_149</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_150</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_154</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>하지만 지금처럼 너가 나를 안좋아한다는데 차마 너를 잡을 수가 없네.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>내가 없는 일상,내가 없는 너의 옆자리, 너는 괜찮아?? 견딜 수 있어??</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">정말 나 매번 너를 잡았는데,, 그건 너가 나를 좋아한다는 마음이 있을때 할 수 있는 일이었어... </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_155</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_156</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_157</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">많이 힘들겠지만 노력해야지.. 아니? 해야만해&lt;np&gt; </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리.. 내일 서로의 일정이 있고, 달려가야 할 길이 있잖아! 일찍 자자 ..</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>안녕 이제 더이상 말하지 않아줬으면 좋겠어. 흔들리고 싶지않아. 이만 끊을게</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_158</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>normalDialogue_Opening_1_1_159</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mindDialogue_Opening_1_1_160</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -654,7 +663,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1013"/>
+  <dimension ref="A1:H1014"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.140625" customWidth="1"/>
@@ -667,7 +676,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -679,116 +688,116 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -797,16 +806,16 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -815,16 +824,16 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -833,16 +842,16 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -851,34 +860,34 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -887,16 +896,16 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -905,16 +914,16 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -923,16 +932,16 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -941,34 +950,34 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -977,34 +986,34 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -1013,16 +1022,16 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -1031,16 +1040,16 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -1048,17 +1057,17 @@
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>13</v>
+      <c r="A22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -1066,71 +1075,71 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1139,16 +1148,16 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1157,16 +1166,16 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -1174,35 +1183,35 @@
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
+      <c r="A29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -1210,10 +1219,18 @@
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
+      <c r="A31" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -1290,14 +1307,14 @@
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="A40" s="7"/>
@@ -1350,14 +1367,14 @@
       <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
       <c r="A46" s="8"/>
@@ -1389,22 +1406,31 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="49" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="51" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="52" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="53" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="54" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="55" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="63" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -2354,6 +2380,7 @@
     <row r="1011" ht="15.75" customHeight="1"/>
     <row r="1012" ht="15.75" customHeight="1"/>
     <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5533D1-38AC-4ED3-B0F6-4EA7BF27F815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BA4CE6-5642-46E9-81C3-168B2E8B6A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1530" windowWidth="28185" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="226">
   <si>
     <t>너도 지금은 집중해야하는 일이 있고, 서로가 서로를 잊기에 충분한 시간일거라고 생각했어.</t>
   </si>
@@ -135,10 +135,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>얼마전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>아니야.. 나는 여전히 내가 그리는 미래에는 너가 그려지지 않아..</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -283,10 +279,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">많이 힘들겠지만 노력해야지.. 아니? 해야만해&lt;np&gt; </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>우리.. 내일 서로의 일정이 있고, 달려가야 할 길이 있잖아! 일찍 자자 ..</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -316,6 +308,7294 @@
   </si>
   <si>
     <t>CharacterDataId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>많이 힘들겠지만 노력해야지.. 아니? 해야만해</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼마 전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Hyunwoo_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_182</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혹시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평소랑 뭔가 다르게 힘들어 보이시는데 무슨 일 있으신가요?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_184</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_183</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아..뭐 별건 아니고 그냥 여자 친구와 헤어졌습니다. 허허</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이고..잠시 밖으로 나갈까요?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_186</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">괜찮습니까.. 제가 위로 같은건 잘 못하지만 그래도 말을 걸어야 할거 같았습니다. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_189</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수업도 좋지만 지금은 쉬는건 어떻겠습니까…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_187</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_190</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉬게 되면은 더 공허하고 고통스러울거 같습니다…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼저 물어봐주셔서 감사합니다…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>알겠습니다.. 그래도 무리는 하지 마십쇼.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_191</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_192</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_204</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>여보세요?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_193</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_205</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕.. 다시 연락해서 미안한데 나 할 말이  아직 남아서 연락했어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_206</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>말해.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하루동안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고민하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>받아들이려고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노력도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해보았는데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아무리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어버버</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헤어진거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>늦은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간이라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못했었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_207</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_208</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>응.. 일단은 나는 할 말 다했고, 들어줄게.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그랬는데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>식게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못인거같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헤어지게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지점까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만든거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짐이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌓이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줬던거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사소한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것들이어도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌓이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌓여서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘든게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>했던거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너한테</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처받은거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짐이라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각한적도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이제는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그만해야할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왔다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말한거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그치만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짚고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>넘어간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었잖아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단순히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제였다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얘기했으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어땠을까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안한데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너랑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진지하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각한적이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너랑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만난것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해본적도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었으니까</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리했고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너랑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미래를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그릴수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없으니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>걸어갈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여자를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾았으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋겠다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_209</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_210</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_211</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_212</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_213</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_214</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_215</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_216</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_217</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_218</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_219</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_220</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_222</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너와의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미래를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈꿨고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헤어짐이라는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들어본</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미래가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바뀌도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노력한다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>아직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이루진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않았지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바뀐다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌아갈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있을까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미래는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어떤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">,  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모습은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어떤것인지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_221</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_227</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_228</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_229</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_230</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_231</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_232</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_233</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_234</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_235</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_236</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_237</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_238</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_239</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_240</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_241</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_242</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_243</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_244</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_245</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_246</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_247</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_248</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_249</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_250</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_251</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_252</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_253</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_254</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_266</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_267</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_268</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_269</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_270</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_271</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_272</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_273</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_275</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_276</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_277</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_278</t>
+  </si>
+  <si>
+    <r>
+      <t>정말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안한데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주절</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주절</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설명하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노력해도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불가능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하다는거네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상황이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>답답해</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명확한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뭐인지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뭐였는지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>될텐데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>막연하게만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헤어지는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사실만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되니까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘드네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고칠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분인거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_229</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동안에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분인거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>??</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>응</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>넌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>될</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없을거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고친다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>될거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안드는거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">... </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스무고개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자꾸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반복되는거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>납득이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안되어서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>납득하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안하고는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나름인거고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>이별이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양방향이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아닐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의무도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물어봤으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋겠어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_254</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_263</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_255</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설명하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싫고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정도라면</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘들고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아팠을거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아무것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모르면서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감정적으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기하고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사실은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싫어서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런거였을텐데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>미안해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋아했어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처음이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되어주어서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고맙고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>죽을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때까지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잊지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않을게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>잘지내고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>열심히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할테니까</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>너도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원하는거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꼭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이루길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사랑해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안녕</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이젠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진짜로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리할게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아프게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_264</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_265</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_274</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>알아줘서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고마워</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋아했던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진심이었어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘자</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자책하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탓이라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해주면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋겠네</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안아팠으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋겠어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>이만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끊을게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안녕</t>
+    </r>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_185</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -323,7 +7603,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -353,6 +7633,32 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -395,7 +7701,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -418,13 +7724,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -445,6 +7825,30 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -717,7 +8121,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -812,10 +8216,10 @@
         <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -833,7 +8237,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -842,7 +8246,7 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>28</v>
@@ -851,7 +8255,7 @@
         <v>30</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -860,7 +8264,7 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>28</v>
@@ -869,7 +8273,7 @@
         <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -878,16 +8282,16 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -896,7 +8300,7 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>22</v>
@@ -905,7 +8309,7 @@
         <v>31</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -914,16 +8318,16 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -932,16 +8336,16 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -950,16 +8354,16 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -968,16 +8372,16 @@
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -986,16 +8390,16 @@
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1004,16 +8408,16 @@
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -1022,16 +8426,16 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -1040,16 +8444,16 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -1058,16 +8462,16 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -1076,7 +8480,7 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
@@ -1085,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -1094,7 +8498,7 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>11</v>
@@ -1103,7 +8507,7 @@
         <v>13</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -1112,16 +8516,16 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1130,16 +8534,16 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1148,16 +8552,16 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1166,16 +8570,16 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -1184,16 +8588,16 @@
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -1202,16 +8606,16 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -1220,16 +8624,16 @@
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -1237,248 +8641,1148 @@
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
+      <c r="A32" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
+      <c r="A33" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
+      <c r="A34" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>225</v>
+      </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="A35" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>89</v>
+      </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+      <c r="A36" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>90</v>
+      </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
+      <c r="A37" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>94</v>
+      </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
+      <c r="A38" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>95</v>
+      </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+      <c r="A39" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="A40" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>99</v>
+      </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="A41" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>101</v>
+      </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="A42" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>105</v>
+      </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+      <c r="A43" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>106</v>
+      </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="A44" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
+      <c r="A45" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>121</v>
+      </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
+      <c r="A46" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>122</v>
+      </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="A47" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>123</v>
+      </c>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="A48" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
+      <c r="A49" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E49" s="20"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="51" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="52" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="53" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="54" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="55" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="56" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="57" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="58" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="60" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="61" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="50" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A50" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E50" s="22"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A51" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="22"/>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A52" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E52" s="22"/>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A53" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E53" s="22"/>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A54" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="22"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A55" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="22"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A56" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E56" s="22"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A57" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E57" s="22"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A58" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E58" s="22"/>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A59" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B59" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59" s="22"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A60" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" s="22"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A61" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="E61" s="22"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A62" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B62" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E62" s="22"/>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A63" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="E63" s="22"/>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A64" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E64" s="22"/>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A65" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" s="22"/>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A66" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66" s="22"/>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A67" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="E67" s="22"/>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A68" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E68" s="22"/>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A69" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E69" s="22"/>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A70" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="E70" s="22"/>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A71" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D71" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="E71" s="22"/>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A72" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E72" s="22"/>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A73" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="E73" s="22"/>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A74" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="E74" s="22"/>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A75" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="E75" s="22"/>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A76" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E76" s="22"/>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A77" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D77" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E77" s="22"/>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A78" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D78" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="E78" s="22"/>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A79" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="E79" s="22"/>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A80" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D80" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="E80" s="22"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A81" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="E81" s="22"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A82" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="D82" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="E82" s="22"/>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A83" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="E83" s="22"/>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A84" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="D84" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E84" s="22"/>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A85" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D85" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="E85" s="22"/>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A86" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="B86" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="D86" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="E86" s="22"/>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A87" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E87" s="22"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A88" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="B88" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D88" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="E88" s="22"/>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A89" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D89" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="E89" s="22"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A90" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="D90" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="E90" s="22"/>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A91" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D91" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="E91" s="22"/>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A92" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B92" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="D92" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E92" s="22"/>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A93" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D93" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="E93" s="22"/>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A94" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B94" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="D94" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E94" s="22"/>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A95" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B95" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D95" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E95" s="22"/>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A96" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B96" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="D96" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E96" s="22"/>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A97" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C97" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="D97" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="E97" s="22"/>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A98" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B98" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D98" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="E98" s="22"/>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A99" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C99" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D99" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E99" s="22"/>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A100" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B100" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C100" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D100" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E100" s="22"/>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A101" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="B101" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="D101" s="27"/>
+      <c r="E101" s="22"/>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A102" s="22"/>
+      <c r="B102" s="22"/>
+      <c r="C102" s="22"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A103" s="22"/>
+      <c r="B103" s="22"/>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A104" s="22"/>
+      <c r="B104" s="22"/>
+      <c r="C104" s="22"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="22"/>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A105" s="22"/>
+      <c r="B105" s="22"/>
+      <c r="C105" s="22"/>
+      <c r="D105" s="22"/>
+      <c r="E105" s="22"/>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A106" s="22"/>
+      <c r="B106" s="22"/>
+      <c r="C106" s="22"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="22"/>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="108" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="109" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="110" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="111" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="112" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="113" ht="15.75" customHeight="1"/>
     <row r="114" ht="15.75" customHeight="1"/>
     <row r="115" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5533D1-38AC-4ED3-B0F6-4EA7BF27F815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FFD56E-FD2F-4E5D-AD13-E2C7B30A7EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="237">
   <si>
     <t>너도 지금은 집중해야하는 일이 있고, 서로가 서로를 잊기에 충분한 시간일거라고 생각했어.</t>
   </si>
   <si>
-    <t>SelectionNameList</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -135,10 +132,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>얼마전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>아니야.. 나는 여전히 내가 그리는 미래에는 너가 그려지지 않아..</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -283,10 +276,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">많이 힘들겠지만 노력해야지.. 아니? 해야만해&lt;np&gt; </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>우리.. 내일 서로의 일정이 있고, 달려가야 할 길이 있잖아! 일찍 자자 ..</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -316,6 +305,7336 @@
   </si>
   <si>
     <t>CharacterDataId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>많이 힘들겠지만 노력해야지.. 아니? 해야만해</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼마 전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Hyunwoo_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_182</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혹시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평소랑 뭔가 다르게 힘들어 보이시는데 무슨 일 있으신가요?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_184</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_183</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아..뭐 별건 아니고 그냥 여자 친구와 헤어졌습니다. 허허</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이고..잠시 밖으로 나갈까요?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_186</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">괜찮습니까.. 제가 위로 같은건 잘 못하지만 그래도 말을 걸어야 할거 같았습니다. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_189</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수업도 좋지만 지금은 쉬는건 어떻겠습니까…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_187</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_190</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉬게 되면은 더 공허하고 고통스러울거 같습니다…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼저 물어봐주셔서 감사합니다…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>알겠습니다.. 그래도 무리는 하지 마십쇼.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_191</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_192</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_204</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>여보세요?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_193</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_205</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕.. 다시 연락해서 미안한데 나 할 말이  아직 남아서 연락했어.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_206</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>말해.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하루동안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고민하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>받아들이려고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노력도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해보았는데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아무리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어버버</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헤어진거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>늦은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간이라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못했었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_207</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_208</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>응.. 일단은 나는 할 말 다했고, 들어줄게.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그랬는데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>식게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못인거같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헤어지게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지점까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만든거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짐이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌓이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줬던거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사소한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것들이어도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌓이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쌓여서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘든게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>했던거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너한테</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처받은거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짐이라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각한적도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이제는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그만해야할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왔다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말한거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그치만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짚고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>넘어간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었잖아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단순히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제였다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얘기했으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어땠을까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안한데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너랑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진지하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각한적이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너랑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결혼할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만난것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해본적도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었으니까</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리했고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너랑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미래를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그릴수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없으니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>걸어갈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여자를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾았으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋겠다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_209</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_210</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_211</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_212</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_213</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_214</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_215</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_216</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_217</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_218</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_219</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_220</t>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_222</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너와의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미래를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈꿨고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헤어짐이라는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들어본</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미래가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바뀌도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노력한다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>아직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이루진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않았지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바뀐다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌아갈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있을까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미래는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어떤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">,  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모습은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어떤것인지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_221</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_227</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_228</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_229</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_230</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_231</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_232</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_233</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_234</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_235</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_236</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_237</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_238</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_239</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_240</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_241</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_242</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_243</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_244</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_245</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_246</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_247</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_248</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_249</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_250</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_251</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_252</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_253</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_254</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_266</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_267</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_268</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_269</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_270</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_271</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_272</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_273</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_275</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_276</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_277</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_278</t>
+  </si>
+  <si>
+    <r>
+      <t>정말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안한데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주절</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주절</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설명하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이미</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노력해도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불가능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하다는거네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상황이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>답답해</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명확한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뭐인지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뭐였는지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이유를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>될텐데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>막연하게만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헤어지는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사실만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되니까</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘드네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고칠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분인거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_229</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동안에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분인거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>??</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>응</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>넌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>될</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없을거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고친다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘못해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>될거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안드는거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">... </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스무고개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자꾸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반복되는거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>납득이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안되어서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>납득하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안하고는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나름인거고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>이별이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양방향이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아닐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는거야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의무도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물어봤으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋겠어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_254</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_263</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_255</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇게까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설명하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싫고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정도라면</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘들고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아팠을거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아무것도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모르면서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감정적으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기하고</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사실은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싫어서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그런거였을텐데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>미안해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋아했어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처음이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되어주어서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고맙고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>죽을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때까지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잊지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않을게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>잘지내고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>열심히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할테니까</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>너도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원하는거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꼭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이루길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사랑해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안녕</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이젠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진짜로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리할게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아프게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_264</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_265</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_274</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>알아줘서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고마워</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋아했던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진심이었어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘자</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자책하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탓이라고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해주면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋겠네</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안아팠으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋겠어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>이만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끊을게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안녕</t>
+    </r>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_185</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGImagePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Call Image</t>
+  </si>
+  <si>
+    <t>Sprite/Call Image</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Class Room</t>
+  </si>
+  <si>
+    <t>Sprite/Out Class</t>
+  </si>
+  <si>
+    <t>Sprite/Class Room</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Out Class cry</t>
+  </si>
+  <si>
+    <t>Sprite/Out Class</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Cu go home</t>
+  </si>
+  <si>
+    <t>Sprite/CU go home cry</t>
+  </si>
+  <si>
+    <t>Sprite/Cu go home</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -323,7 +7642,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -353,6 +7672,32 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -395,7 +7740,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -418,13 +7763,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -445,6 +7903,45 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -676,7 +8173,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -688,797 +8185,1899 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
+      <c r="G3" s="36" t="s">
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="E4" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="22"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="35"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="E5" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="22"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="E6" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="22"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="E7" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="35"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="D17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="5"/>
+        <v>49</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" s="6"/>
+      <c r="E30" s="6" t="s">
+        <v>227</v>
+      </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="6"/>
+      <c r="E31" s="6" t="s">
+        <v>227</v>
+      </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+      <c r="A32" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>231</v>
+      </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
+      <c r="A33" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>229</v>
+      </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
+      <c r="A34" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>229</v>
+      </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="A35" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>233</v>
+      </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
+      <c r="A36" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>232</v>
+      </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
+      <c r="A37" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>233</v>
+      </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
+      <c r="A38" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>230</v>
+      </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
+      <c r="A39" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>230</v>
+      </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+      <c r="A40" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="A41" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
+      <c r="A42" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
+      <c r="A43" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
+      <c r="A44" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
+      <c r="A45" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
+      <c r="A46" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>234</v>
+      </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
+      <c r="A47" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>234</v>
+      </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
+      <c r="A48" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>234</v>
+      </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
+      <c r="A49" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>234</v>
+      </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="51" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="52" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="53" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="54" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="55" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="56" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="57" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="58" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="60" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="61" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="50" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A50" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A51" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A52" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A53" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A54" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A55" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A56" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B56" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A57" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A58" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A59" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A60" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A61" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A62" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A63" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A64" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="E64" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A65" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A66" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A67" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A68" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A69" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A70" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A71" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="D71" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A72" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="D72" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="E72" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A73" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="D73" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A74" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A75" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A76" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A77" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D77" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A78" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="D78" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="E78" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A79" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A80" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="E80" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A81" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A82" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A83" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="E83" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A84" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B84" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D84" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="E84" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A85" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="D85" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A86" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="B86" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D86" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="E86" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A87" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="E87" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A88" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D88" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E88" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A89" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D89" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="E89" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A90" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="D90" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="E90" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A91" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D91" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="E91" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A92" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="B92" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="D92" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="E92" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A93" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="D93" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E93" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A94" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B94" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D94" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="E94" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A95" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B95" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="D95" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E95" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A96" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B96" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D96" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E96" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A97" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="D97" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E97" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A98" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B98" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="D98" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="E98" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A99" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C99" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D99" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="E99" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A100" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="B100" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="D100" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E100" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A101" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="D101" s="27"/>
+      <c r="E101" s="22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A102" s="22"/>
+      <c r="B102" s="22"/>
+      <c r="C102" s="22"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A103" s="22"/>
+      <c r="B103" s="22"/>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A104" s="22"/>
+      <c r="B104" s="22"/>
+      <c r="C104" s="22"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="22"/>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A105" s="22"/>
+      <c r="B105" s="22"/>
+      <c r="C105" s="22"/>
+      <c r="D105" s="22"/>
+      <c r="E105" s="22"/>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A106" s="22"/>
+      <c r="B106" s="22"/>
+      <c r="C106" s="22"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="22"/>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="108" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="109" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="110" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="111" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="112" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="113" ht="15.75" customHeight="1"/>
     <row r="114" ht="15.75" customHeight="1"/>
     <row r="115" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FFD56E-FD2F-4E5D-AD13-E2C7B30A7EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A838B0AC-8E7D-4729-8B3C-7928ABD013E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="238">
   <si>
     <t>너도 지금은 집중해야하는 일이 있고, 서로가 서로를 잊기에 충분한 시간일거라고 생각했어.</t>
   </si>
@@ -7635,6 +7635,10 @@
   </si>
   <si>
     <t>Sprite/Cu go home</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_279</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -10032,7 +10036,9 @@
       <c r="C101" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="D101" s="27"/>
+      <c r="D101" s="27" t="s">
+        <v>237</v>
+      </c>
       <c r="E101" s="22" t="s">
         <v>234</v>
       </c>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A838B0AC-8E7D-4729-8B3C-7928ABD013E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A838B0AC-8E7D-4729-8B3C-7928ABD013E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968F1539-5DC7-4925-A913-C4E9D5C62D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="270">
   <si>
     <t>너도 지금은 집중해야하는 일이 있고, 서로가 서로를 잊기에 충분한 시간일거라고 생각했어.</t>
   </si>
@@ -7639,6 +7639,173 @@
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_279</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Jooyoung_01</t>
+  </si>
+  <si>
+    <t>character_Jooyoung_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_278</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_293</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시 반 넘었는데 아직도 아직도 안씻고 뭐하니…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_294</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 준비하려고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐냐 너 혹시 울었냐?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Sister1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/cheer up Sister</t>
+  </si>
+  <si>
+    <t>아 씻을게 나가 …</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸핰 헤어졌나보네</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>에휴 둘이 없으면 안될거처럼 그러더니 에잉 쯧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_295</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_296</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_297</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_298</t>
+  </si>
+  <si>
+    <t>Sprite/Sister2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무튼 정신차리고 나와. 엄마가 학원 데려다 주래.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_298</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_299</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_299</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_300</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>됐어. 오늘부터 뛰어갈거야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음대로 해라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">~ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>난 간다잉</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_301</t>
+  </si>
+  <si>
+    <t>Sprite/Sister3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Sister4</t>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_302</t>
+  </si>
+  <si>
+    <t>Sprite/morning Emptyroom</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_303</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -7744,7 +7911,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -7880,13 +8047,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -7946,6 +8133,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -10028,7 +10218,7 @@
     </row>
     <row r="101" spans="1:5" ht="15.75" customHeight="1">
       <c r="A101" s="27" t="s">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="B101" s="27" t="s">
         <v>27</v>
@@ -10044,158 +10234,900 @@
       </c>
     </row>
     <row r="102" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A102" s="22"/>
-      <c r="B102" s="22"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="22"/>
+      <c r="A102" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="B102" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="C102" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="D102" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="E102" s="22" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="103" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A103" s="22"/>
-      <c r="B103" s="22"/>
-      <c r="C103" s="22"/>
-      <c r="D103" s="22"/>
-      <c r="E103" s="22"/>
+      <c r="A103" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="B103" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C103" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="D103" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="E103" s="22" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="104" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A104" s="22"/>
-      <c r="B104" s="22"/>
-      <c r="C104" s="22"/>
-      <c r="D104" s="22"/>
-      <c r="E104" s="22"/>
+      <c r="A104" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="B104" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="C104" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="D104" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="E104" s="27" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="105" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A105" s="22"/>
-      <c r="B105" s="22"/>
-      <c r="C105" s="22"/>
-      <c r="D105" s="22"/>
-      <c r="E105" s="22"/>
+      <c r="A105" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="B105" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="D105" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="E105" s="27" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="106" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A106" s="22"/>
-      <c r="B106" s="22"/>
-      <c r="C106" s="22"/>
-      <c r="D106" s="22"/>
-      <c r="E106" s="22"/>
-    </row>
-    <row r="107" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="108" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="109" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="110" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="111" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="112" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
+      <c r="A106" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="C106" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="D106" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="E106" s="27" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A107" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="B107" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="C107" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="D107" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E107" s="41" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A108" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="B108" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="C108" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="D108" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="E108" s="27" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A109" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="D109" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="E109" s="27" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A110" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="B110" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="C110" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="D110" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="E110" s="22" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A111" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="D111" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="E111" s="27" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A112" s="40"/>
+      <c r="B112" s="22"/>
+      <c r="C112" s="22"/>
+      <c r="D112" s="22"/>
+      <c r="E112" s="22"/>
+    </row>
+    <row r="113" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A113" s="27"/>
+      <c r="B113" s="22"/>
+      <c r="C113" s="22"/>
+      <c r="D113" s="22"/>
+      <c r="E113" s="22"/>
+    </row>
+    <row r="114" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A114" s="22"/>
+      <c r="B114" s="22"/>
+      <c r="C114" s="22"/>
+      <c r="D114" s="22"/>
+      <c r="E114" s="22"/>
+    </row>
+    <row r="115" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A115" s="22"/>
+      <c r="B115" s="22"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+    </row>
+    <row r="116" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A116" s="22"/>
+      <c r="B116" s="22"/>
+      <c r="C116" s="22"/>
+      <c r="D116" s="22"/>
+      <c r="E116" s="22"/>
+    </row>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A117" s="22"/>
+      <c r="B117" s="22"/>
+      <c r="C117" s="22"/>
+      <c r="D117" s="22"/>
+      <c r="E117" s="22"/>
+    </row>
+    <row r="118" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A118" s="22"/>
+      <c r="B118" s="22"/>
+      <c r="C118" s="22"/>
+      <c r="D118" s="22"/>
+      <c r="E118" s="22"/>
+    </row>
+    <row r="119" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A119" s="22"/>
+      <c r="B119" s="22"/>
+      <c r="C119" s="22"/>
+      <c r="D119" s="22"/>
+      <c r="E119" s="22"/>
+    </row>
+    <row r="120" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A120" s="22"/>
+      <c r="B120" s="22"/>
+      <c r="C120" s="22"/>
+      <c r="D120" s="22"/>
+      <c r="E120" s="22"/>
+    </row>
+    <row r="121" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A121" s="22"/>
+      <c r="B121" s="22"/>
+      <c r="C121" s="22"/>
+      <c r="D121" s="22"/>
+      <c r="E121" s="22"/>
+    </row>
+    <row r="122" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A122" s="22"/>
+      <c r="B122" s="22"/>
+      <c r="C122" s="22"/>
+      <c r="D122" s="22"/>
+      <c r="E122" s="22"/>
+    </row>
+    <row r="123" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A123" s="22"/>
+      <c r="B123" s="22"/>
+      <c r="C123" s="22"/>
+      <c r="D123" s="22"/>
+      <c r="E123" s="22"/>
+    </row>
+    <row r="124" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A124" s="22"/>
+      <c r="B124" s="22"/>
+      <c r="C124" s="22"/>
+      <c r="D124" s="22"/>
+      <c r="E124" s="22"/>
+    </row>
+    <row r="125" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A125" s="22"/>
+      <c r="B125" s="22"/>
+      <c r="C125" s="22"/>
+      <c r="D125" s="22"/>
+      <c r="E125" s="22"/>
+    </row>
+    <row r="126" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A126" s="22"/>
+      <c r="B126" s="22"/>
+      <c r="C126" s="22"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="22"/>
+    </row>
+    <row r="127" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A127" s="22"/>
+      <c r="B127" s="22"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A128" s="22"/>
+      <c r="B128" s="22"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="22"/>
+      <c r="E128" s="22"/>
+    </row>
+    <row r="129" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A129" s="22"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+    </row>
+    <row r="130" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A130" s="22"/>
+      <c r="B130" s="22"/>
+      <c r="C130" s="22"/>
+      <c r="D130" s="22"/>
+      <c r="E130" s="22"/>
+    </row>
+    <row r="131" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A131" s="22"/>
+      <c r="B131" s="22"/>
+      <c r="C131" s="22"/>
+      <c r="D131" s="22"/>
+      <c r="E131" s="22"/>
+    </row>
+    <row r="132" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A132" s="22"/>
+      <c r="B132" s="22"/>
+      <c r="C132" s="22"/>
+      <c r="D132" s="22"/>
+      <c r="E132" s="22"/>
+    </row>
+    <row r="133" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A133" s="22"/>
+      <c r="B133" s="22"/>
+      <c r="C133" s="22"/>
+      <c r="D133" s="22"/>
+      <c r="E133" s="22"/>
+    </row>
+    <row r="134" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A134" s="22"/>
+      <c r="B134" s="22"/>
+      <c r="C134" s="22"/>
+      <c r="D134" s="22"/>
+      <c r="E134" s="22"/>
+    </row>
+    <row r="135" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A135" s="22"/>
+      <c r="B135" s="22"/>
+      <c r="C135" s="22"/>
+      <c r="D135" s="22"/>
+      <c r="E135" s="22"/>
+    </row>
+    <row r="136" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A136" s="22"/>
+      <c r="B136" s="22"/>
+      <c r="C136" s="22"/>
+      <c r="D136" s="22"/>
+      <c r="E136" s="22"/>
+    </row>
+    <row r="137" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A137" s="22"/>
+      <c r="B137" s="22"/>
+      <c r="C137" s="22"/>
+      <c r="D137" s="22"/>
+      <c r="E137" s="22"/>
+    </row>
+    <row r="138" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A138" s="22"/>
+      <c r="B138" s="22"/>
+      <c r="C138" s="22"/>
+      <c r="D138" s="22"/>
+      <c r="E138" s="22"/>
+    </row>
+    <row r="139" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A139" s="22"/>
+      <c r="B139" s="22"/>
+      <c r="C139" s="22"/>
+      <c r="D139" s="22"/>
+      <c r="E139" s="22"/>
+    </row>
+    <row r="140" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A140" s="22"/>
+      <c r="B140" s="22"/>
+      <c r="C140" s="22"/>
+      <c r="D140" s="22"/>
+      <c r="E140" s="22"/>
+    </row>
+    <row r="141" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A141" s="22"/>
+      <c r="B141" s="22"/>
+      <c r="C141" s="22"/>
+      <c r="D141" s="22"/>
+      <c r="E141" s="22"/>
+    </row>
+    <row r="142" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A142" s="22"/>
+      <c r="B142" s="22"/>
+      <c r="C142" s="22"/>
+      <c r="D142" s="22"/>
+      <c r="E142" s="22"/>
+    </row>
+    <row r="143" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A143" s="22"/>
+      <c r="B143" s="22"/>
+      <c r="C143" s="22"/>
+      <c r="D143" s="22"/>
+      <c r="E143" s="22"/>
+    </row>
+    <row r="144" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A144" s="22"/>
+      <c r="B144" s="22"/>
+      <c r="C144" s="22"/>
+      <c r="D144" s="22"/>
+      <c r="E144" s="22"/>
+    </row>
+    <row r="145" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A145" s="22"/>
+      <c r="B145" s="22"/>
+      <c r="C145" s="22"/>
+      <c r="D145" s="22"/>
+      <c r="E145" s="22"/>
+    </row>
+    <row r="146" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A146" s="22"/>
+      <c r="B146" s="22"/>
+      <c r="C146" s="22"/>
+      <c r="D146" s="22"/>
+      <c r="E146" s="22"/>
+    </row>
+    <row r="147" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A147" s="22"/>
+      <c r="B147" s="22"/>
+      <c r="C147" s="22"/>
+      <c r="D147" s="22"/>
+      <c r="E147" s="22"/>
+    </row>
+    <row r="148" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A148" s="22"/>
+      <c r="B148" s="22"/>
+      <c r="C148" s="22"/>
+      <c r="D148" s="22"/>
+      <c r="E148" s="22"/>
+    </row>
+    <row r="149" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A149" s="22"/>
+      <c r="B149" s="22"/>
+      <c r="C149" s="22"/>
+      <c r="D149" s="22"/>
+      <c r="E149" s="22"/>
+    </row>
+    <row r="150" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A150" s="22"/>
+      <c r="B150" s="22"/>
+      <c r="C150" s="22"/>
+      <c r="D150" s="22"/>
+      <c r="E150" s="22"/>
+    </row>
+    <row r="151" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A151" s="22"/>
+      <c r="B151" s="22"/>
+      <c r="C151" s="22"/>
+      <c r="D151" s="22"/>
+      <c r="E151" s="22"/>
+    </row>
+    <row r="152" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A152" s="22"/>
+      <c r="B152" s="22"/>
+      <c r="C152" s="22"/>
+      <c r="D152" s="22"/>
+      <c r="E152" s="22"/>
+    </row>
+    <row r="153" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A153" s="22"/>
+      <c r="B153" s="22"/>
+      <c r="C153" s="22"/>
+      <c r="D153" s="22"/>
+      <c r="E153" s="22"/>
+    </row>
+    <row r="154" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A154" s="22"/>
+      <c r="B154" s="22"/>
+      <c r="C154" s="22"/>
+      <c r="D154" s="22"/>
+      <c r="E154" s="22"/>
+    </row>
+    <row r="155" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A155" s="22"/>
+      <c r="B155" s="22"/>
+      <c r="C155" s="22"/>
+      <c r="D155" s="22"/>
+      <c r="E155" s="22"/>
+    </row>
+    <row r="156" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A156" s="22"/>
+      <c r="B156" s="22"/>
+      <c r="C156" s="22"/>
+      <c r="D156" s="22"/>
+      <c r="E156" s="22"/>
+    </row>
+    <row r="157" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A157" s="22"/>
+      <c r="B157" s="22"/>
+      <c r="C157" s="22"/>
+      <c r="D157" s="22"/>
+      <c r="E157" s="22"/>
+    </row>
+    <row r="158" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A158" s="22"/>
+      <c r="B158" s="22"/>
+      <c r="C158" s="22"/>
+      <c r="D158" s="22"/>
+      <c r="E158" s="22"/>
+    </row>
+    <row r="159" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A159" s="22"/>
+      <c r="B159" s="22"/>
+      <c r="C159" s="22"/>
+      <c r="D159" s="22"/>
+      <c r="E159" s="22"/>
+    </row>
+    <row r="160" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A160" s="22"/>
+      <c r="B160" s="22"/>
+      <c r="C160" s="22"/>
+      <c r="D160" s="22"/>
+      <c r="E160" s="22"/>
+    </row>
+    <row r="161" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A161" s="22"/>
+      <c r="B161" s="22"/>
+      <c r="C161" s="22"/>
+      <c r="D161" s="22"/>
+      <c r="E161" s="22"/>
+    </row>
+    <row r="162" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A162" s="22"/>
+      <c r="B162" s="22"/>
+      <c r="C162" s="22"/>
+      <c r="D162" s="22"/>
+      <c r="E162" s="22"/>
+    </row>
+    <row r="163" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A163" s="22"/>
+      <c r="B163" s="22"/>
+      <c r="C163" s="22"/>
+      <c r="D163" s="22"/>
+      <c r="E163" s="22"/>
+    </row>
+    <row r="164" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A164" s="22"/>
+      <c r="B164" s="22"/>
+      <c r="C164" s="22"/>
+      <c r="D164" s="22"/>
+      <c r="E164" s="22"/>
+    </row>
+    <row r="165" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A165" s="22"/>
+      <c r="B165" s="22"/>
+      <c r="C165" s="22"/>
+      <c r="D165" s="22"/>
+      <c r="E165" s="22"/>
+    </row>
+    <row r="166" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A166" s="22"/>
+      <c r="B166" s="22"/>
+      <c r="C166" s="22"/>
+      <c r="D166" s="22"/>
+      <c r="E166" s="22"/>
+    </row>
+    <row r="167" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A167" s="22"/>
+      <c r="B167" s="22"/>
+      <c r="C167" s="22"/>
+      <c r="D167" s="22"/>
+      <c r="E167" s="22"/>
+    </row>
+    <row r="168" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A168" s="22"/>
+      <c r="B168" s="22"/>
+      <c r="C168" s="22"/>
+      <c r="D168" s="22"/>
+      <c r="E168" s="22"/>
+    </row>
+    <row r="169" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A169" s="22"/>
+      <c r="B169" s="22"/>
+      <c r="C169" s="22"/>
+      <c r="D169" s="22"/>
+      <c r="E169" s="22"/>
+    </row>
+    <row r="170" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A170" s="22"/>
+      <c r="B170" s="22"/>
+      <c r="C170" s="22"/>
+      <c r="D170" s="22"/>
+      <c r="E170" s="22"/>
+    </row>
+    <row r="171" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A171" s="22"/>
+      <c r="B171" s="22"/>
+      <c r="C171" s="22"/>
+      <c r="D171" s="22"/>
+      <c r="E171" s="22"/>
+    </row>
+    <row r="172" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A172" s="22"/>
+      <c r="B172" s="22"/>
+      <c r="C172" s="22"/>
+      <c r="D172" s="22"/>
+      <c r="E172" s="22"/>
+    </row>
+    <row r="173" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A173" s="22"/>
+      <c r="B173" s="22"/>
+      <c r="C173" s="22"/>
+      <c r="D173" s="22"/>
+      <c r="E173" s="22"/>
+    </row>
+    <row r="174" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A174" s="22"/>
+      <c r="B174" s="22"/>
+      <c r="C174" s="22"/>
+      <c r="D174" s="22"/>
+      <c r="E174" s="22"/>
+    </row>
+    <row r="175" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A175" s="22"/>
+      <c r="B175" s="22"/>
+      <c r="C175" s="22"/>
+      <c r="D175" s="22"/>
+      <c r="E175" s="22"/>
+    </row>
+    <row r="176" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A176" s="22"/>
+      <c r="B176" s="22"/>
+      <c r="C176" s="22"/>
+      <c r="D176" s="22"/>
+      <c r="E176" s="22"/>
+    </row>
+    <row r="177" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A177" s="22"/>
+      <c r="B177" s="22"/>
+      <c r="C177" s="22"/>
+      <c r="D177" s="22"/>
+      <c r="E177" s="22"/>
+    </row>
+    <row r="178" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A178" s="22"/>
+      <c r="B178" s="22"/>
+      <c r="C178" s="22"/>
+      <c r="D178" s="22"/>
+      <c r="E178" s="22"/>
+    </row>
+    <row r="179" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A179" s="22"/>
+      <c r="B179" s="22"/>
+      <c r="C179" s="22"/>
+      <c r="D179" s="22"/>
+      <c r="E179" s="22"/>
+    </row>
+    <row r="180" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A180" s="22"/>
+      <c r="B180" s="22"/>
+      <c r="C180" s="22"/>
+      <c r="D180" s="22"/>
+      <c r="E180" s="22"/>
+    </row>
+    <row r="181" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A181" s="22"/>
+      <c r="B181" s="22"/>
+      <c r="C181" s="22"/>
+      <c r="D181" s="22"/>
+      <c r="E181" s="22"/>
+    </row>
+    <row r="182" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A182" s="22"/>
+      <c r="B182" s="22"/>
+      <c r="C182" s="22"/>
+      <c r="D182" s="22"/>
+      <c r="E182" s="22"/>
+    </row>
+    <row r="183" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A183" s="22"/>
+      <c r="B183" s="22"/>
+      <c r="C183" s="22"/>
+      <c r="D183" s="22"/>
+      <c r="E183" s="22"/>
+    </row>
+    <row r="184" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A184" s="22"/>
+      <c r="B184" s="22"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="22"/>
+      <c r="E184" s="22"/>
+    </row>
+    <row r="185" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A185" s="22"/>
+      <c r="B185" s="22"/>
+      <c r="C185" s="22"/>
+      <c r="D185" s="22"/>
+      <c r="E185" s="22"/>
+    </row>
+    <row r="186" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A186" s="22"/>
+      <c r="B186" s="22"/>
+      <c r="C186" s="22"/>
+      <c r="D186" s="22"/>
+      <c r="E186" s="22"/>
+    </row>
+    <row r="187" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A187" s="22"/>
+      <c r="B187" s="22"/>
+      <c r="C187" s="22"/>
+      <c r="D187" s="22"/>
+      <c r="E187" s="22"/>
+    </row>
+    <row r="188" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A188" s="22"/>
+      <c r="B188" s="22"/>
+      <c r="C188" s="22"/>
+      <c r="D188" s="22"/>
+      <c r="E188" s="22"/>
+    </row>
+    <row r="189" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A189" s="22"/>
+      <c r="B189" s="22"/>
+      <c r="C189" s="22"/>
+      <c r="D189" s="22"/>
+      <c r="E189" s="22"/>
+    </row>
+    <row r="190" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A190" s="22"/>
+      <c r="B190" s="22"/>
+      <c r="C190" s="22"/>
+      <c r="D190" s="22"/>
+      <c r="E190" s="22"/>
+    </row>
+    <row r="191" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A191" s="22"/>
+      <c r="B191" s="22"/>
+      <c r="C191" s="22"/>
+      <c r="D191" s="22"/>
+      <c r="E191" s="22"/>
+    </row>
+    <row r="192" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A192" s="22"/>
+      <c r="B192" s="22"/>
+      <c r="C192" s="22"/>
+      <c r="D192" s="22"/>
+      <c r="E192" s="22"/>
+    </row>
+    <row r="193" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A193" s="22"/>
+      <c r="B193" s="22"/>
+      <c r="C193" s="22"/>
+      <c r="D193" s="22"/>
+      <c r="E193" s="22"/>
+    </row>
+    <row r="194" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A194" s="22"/>
+      <c r="B194" s="22"/>
+      <c r="C194" s="22"/>
+      <c r="D194" s="22"/>
+      <c r="E194" s="22"/>
+    </row>
+    <row r="195" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A195" s="22"/>
+      <c r="B195" s="22"/>
+      <c r="C195" s="22"/>
+      <c r="D195" s="22"/>
+      <c r="E195" s="22"/>
+    </row>
+    <row r="196" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A196" s="22"/>
+      <c r="B196" s="22"/>
+      <c r="C196" s="22"/>
+      <c r="D196" s="22"/>
+      <c r="E196" s="22"/>
+    </row>
+    <row r="197" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A197" s="22"/>
+      <c r="B197" s="22"/>
+      <c r="C197" s="22"/>
+      <c r="D197" s="22"/>
+      <c r="E197" s="22"/>
+    </row>
+    <row r="198" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A198" s="22"/>
+      <c r="B198" s="22"/>
+      <c r="C198" s="22"/>
+      <c r="D198" s="22"/>
+      <c r="E198" s="22"/>
+    </row>
+    <row r="199" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A199" s="22"/>
+      <c r="B199" s="22"/>
+      <c r="C199" s="22"/>
+      <c r="D199" s="22"/>
+      <c r="E199" s="22"/>
+    </row>
+    <row r="200" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A200" s="22"/>
+      <c r="B200" s="22"/>
+      <c r="C200" s="22"/>
+      <c r="D200" s="22"/>
+      <c r="E200" s="22"/>
+    </row>
+    <row r="201" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A201" s="22"/>
+      <c r="B201" s="22"/>
+      <c r="C201" s="22"/>
+      <c r="D201" s="22"/>
+      <c r="E201" s="22"/>
+    </row>
+    <row r="202" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A202" s="22"/>
+      <c r="B202" s="22"/>
+      <c r="C202" s="22"/>
+      <c r="D202" s="22"/>
+      <c r="E202" s="22"/>
+    </row>
+    <row r="203" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A203" s="22"/>
+      <c r="B203" s="22"/>
+      <c r="C203" s="22"/>
+      <c r="D203" s="22"/>
+      <c r="E203" s="22"/>
+    </row>
+    <row r="204" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A204" s="22"/>
+      <c r="B204" s="22"/>
+      <c r="C204" s="22"/>
+      <c r="D204" s="22"/>
+      <c r="E204" s="22"/>
+    </row>
+    <row r="205" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A205" s="22"/>
+      <c r="B205" s="22"/>
+      <c r="C205" s="22"/>
+      <c r="D205" s="22"/>
+      <c r="E205" s="22"/>
+    </row>
+    <row r="206" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A206" s="22"/>
+      <c r="B206" s="22"/>
+      <c r="C206" s="22"/>
+      <c r="D206" s="22"/>
+      <c r="E206" s="22"/>
+    </row>
+    <row r="207" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A207" s="22"/>
+      <c r="B207" s="22"/>
+      <c r="C207" s="22"/>
+      <c r="D207" s="22"/>
+      <c r="E207" s="22"/>
+    </row>
+    <row r="208" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A208" s="22"/>
+      <c r="B208" s="22"/>
+      <c r="C208" s="22"/>
+      <c r="D208" s="22"/>
+      <c r="E208" s="22"/>
+    </row>
+    <row r="209" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A209" s="22"/>
+      <c r="B209" s="22"/>
+      <c r="C209" s="22"/>
+      <c r="D209" s="22"/>
+      <c r="E209" s="22"/>
+    </row>
+    <row r="210" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A210" s="22"/>
+      <c r="B210" s="22"/>
+      <c r="C210" s="22"/>
+      <c r="D210" s="22"/>
+      <c r="E210" s="22"/>
+    </row>
+    <row r="211" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A211" s="22"/>
+      <c r="B211" s="22"/>
+      <c r="C211" s="22"/>
+      <c r="D211" s="22"/>
+      <c r="E211" s="22"/>
+    </row>
+    <row r="212" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A212" s="22"/>
+      <c r="B212" s="22"/>
+      <c r="C212" s="22"/>
+      <c r="D212" s="22"/>
+      <c r="E212" s="22"/>
+    </row>
+    <row r="213" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A213" s="22"/>
+      <c r="B213" s="22"/>
+      <c r="C213" s="22"/>
+      <c r="D213" s="22"/>
+      <c r="E213" s="22"/>
+    </row>
+    <row r="214" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="215" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="216" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="217" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="218" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="219" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="220" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="221" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="222" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="223" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="224" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968F1539-5DC7-4925-A913-C4E9D5C62D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -8134,8 +8134,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968F1539-5DC7-4925-A913-C4E9D5C62D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5282A163-C0A3-4A0D-A16C-45194CF649A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="319">
   <si>
     <t>너도 지금은 집중해야하는 일이 있고, 서로가 서로를 잊기에 충분한 시간일거라고 생각했어.</t>
   </si>
@@ -7806,6 +7806,352 @@
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_303</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Opening_1_1_302</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보자고해서 미안해.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그렇지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너에게 변화된 모습을 보여주고 싶었어.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어떻게 생각해?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_7</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_8</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_9</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_10</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_11</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_12</t>
+  </si>
+  <si>
+    <t>정말.. 미안한데…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 마음 먹었고, 나는 너와 다시 만날 생각이 없어…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미안해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇구나..또 아프게해서 미안해</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>꼭 잘살아야해!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고마워…넌 좋은 사람이니까. 화이팅했으면 좋겠어. 안녕</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_13</t>
+  </si>
+  <si>
+    <t>Sprite/EndingImage4</t>
+  </si>
+  <si>
+    <t>Sprite/EndingImage4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_5</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_7</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_8</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_9</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_10</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_11</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_12</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_13</t>
+  </si>
+  <si>
+    <t>안녕! 다시 보고 싶었어..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤어지고 나서 열심히 살았고, 너와 미래를 더 꿈꾸고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>떳떳한 사람이 되고 싶어서 노력했어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너는 어떻게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사실 나도.. 너가 없으면 안될거 같더라</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘들고, 너가 너무 보고 싶었어.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다시 보러와줘서 고마워</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리 함께 미래를 꿈꾸고 열심히 살아보자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나도 너와의 미래를 꿈꾸고, 사랑하며 살아가고 싶어!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 생각이야. 행복하게 살아보자!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/EndingImage6</t>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_2_14</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -10388,7 +10734,7 @@
     </row>
     <row r="111" spans="1:5" ht="15.75" customHeight="1">
       <c r="A111" s="27" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B111" s="27" t="s">
         <v>27</v>
@@ -10404,137 +10750,327 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A112" s="40"/>
-      <c r="B112" s="22"/>
-      <c r="C112" s="22"/>
-      <c r="D112" s="22"/>
-      <c r="E112" s="22"/>
+      <c r="A112" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="B112" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="D112" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="E112" s="27" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="113" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A113" s="27"/>
-      <c r="B113" s="22"/>
-      <c r="C113" s="22"/>
-      <c r="D113" s="22"/>
-      <c r="E113" s="22"/>
+      <c r="A113" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="B113" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C113" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="D113" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="E113" s="27" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="114" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A114" s="22"/>
-      <c r="B114" s="22"/>
-      <c r="C114" s="22"/>
-      <c r="D114" s="22"/>
-      <c r="E114" s="22"/>
+      <c r="A114" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="B114" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C114" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="D114" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="E114" s="22" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="115" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A115" s="22"/>
-      <c r="B115" s="22"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="22"/>
-      <c r="E115" s="22"/>
+      <c r="A115" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" s="39" t="s">
+        <v>283</v>
+      </c>
+      <c r="D115" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="116" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A116" s="22"/>
-      <c r="B116" s="22"/>
-      <c r="C116" s="22"/>
-      <c r="D116" s="22"/>
-      <c r="E116" s="22"/>
+      <c r="A116" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="B116" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="D116" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="117" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A117" s="22"/>
-      <c r="B117" s="22"/>
-      <c r="C117" s="22"/>
-      <c r="D117" s="22"/>
-      <c r="E117" s="22"/>
+      <c r="A117" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="D117" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="118" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A118" s="22"/>
-      <c r="B118" s="22"/>
-      <c r="C118" s="22"/>
-      <c r="D118" s="22"/>
-      <c r="E118" s="22"/>
+      <c r="A118" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="B118" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="D118" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="119" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A119" s="22"/>
-      <c r="B119" s="22"/>
-      <c r="C119" s="22"/>
-      <c r="D119" s="22"/>
-      <c r="E119" s="22"/>
+      <c r="A119" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C119" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="D119" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="E119" s="22" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="120" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A120" s="22"/>
-      <c r="B120" s="22"/>
-      <c r="C120" s="22"/>
-      <c r="D120" s="22"/>
-      <c r="E120" s="22"/>
+      <c r="A120" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="B120" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C120" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="D120" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="121" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A121" s="22"/>
-      <c r="B121" s="22"/>
-      <c r="C121" s="22"/>
-      <c r="D121" s="22"/>
-      <c r="E121" s="22"/>
+      <c r="A121" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="B121" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="D121" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="122" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A122" s="22"/>
-      <c r="B122" s="22"/>
-      <c r="C122" s="22"/>
-      <c r="D122" s="22"/>
-      <c r="E122" s="22"/>
+      <c r="A122" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C122" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="D122" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="E122" s="27" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="123" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A123" s="22"/>
-      <c r="B123" s="22"/>
-      <c r="C123" s="22"/>
-      <c r="D123" s="22"/>
-      <c r="E123" s="22"/>
+      <c r="A123" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C123" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="D123" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="E123" s="27" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="124" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A124" s="22"/>
-      <c r="B124" s="22"/>
-      <c r="C124" s="22"/>
-      <c r="D124" s="22"/>
-      <c r="E124" s="22"/>
+      <c r="A124" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C124" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="D124" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="125" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A125" s="22"/>
-      <c r="B125" s="22"/>
-      <c r="C125" s="22"/>
-      <c r="D125" s="22"/>
-      <c r="E125" s="22"/>
+      <c r="A125" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C125" s="39" t="s">
+        <v>307</v>
+      </c>
+      <c r="D125" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="E125" s="27" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="126" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A126" s="22"/>
-      <c r="B126" s="22"/>
-      <c r="C126" s="22"/>
-      <c r="D126" s="22"/>
-      <c r="E126" s="22"/>
+      <c r="A126" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C126" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="D126" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="E126" s="27" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="127" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A127" s="22"/>
-      <c r="B127" s="22"/>
-      <c r="C127" s="22"/>
-      <c r="D127" s="22"/>
-      <c r="E127" s="22"/>
+      <c r="A127" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="B127" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C127" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="D127" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="E127" s="27" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="128" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A128" s="22"/>
-      <c r="B128" s="22"/>
-      <c r="C128" s="22"/>
-      <c r="D128" s="22"/>
-      <c r="E128" s="22"/>
+      <c r="A128" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="B128" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C128" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="D128" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="E128" s="22" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="129" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A129" s="22"/>
-      <c r="B129" s="22"/>
-      <c r="C129" s="22"/>
-      <c r="D129" s="22"/>
-      <c r="E129" s="22"/>
+      <c r="A129" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="D129" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="E129" s="22" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="130" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A130" s="22"/>
-      <c r="B130" s="22"/>
-      <c r="C130" s="22"/>
-      <c r="D130" s="22"/>
-      <c r="E130" s="22"/>
+      <c r="A130" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B130" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="D130" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="E130" s="22" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="131" spans="1:5" ht="15.75" customHeight="1">
       <c r="A131" s="22"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5282A163-C0A3-4A0D-A16C-45194CF649A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4D0BAE-1568-4823-9E0A-3A69A7C37A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7981,9 +7981,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>normalDialogue_Ending_1_1_13</t>
-  </si>
-  <si>
     <t>Sprite/EndingImage4</t>
   </si>
   <si>
@@ -8152,6 +8149,10 @@
   </si>
   <si>
     <t>mindDialogue_Ending_1_2_14</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Ending_1_1_13</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -10763,7 +10764,7 @@
         <v>275</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="15.75" customHeight="1">
@@ -10780,7 +10781,7 @@
         <v>276</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15.75" customHeight="1">
@@ -10797,7 +10798,7 @@
         <v>277</v>
       </c>
       <c r="E114" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="15.75" customHeight="1">
@@ -10814,7 +10815,7 @@
         <v>278</v>
       </c>
       <c r="E115" s="27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15.75" customHeight="1">
@@ -10831,7 +10832,7 @@
         <v>279</v>
       </c>
       <c r="E116" s="27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15.75" customHeight="1">
@@ -10848,7 +10849,7 @@
         <v>280</v>
       </c>
       <c r="E117" s="27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15.75" customHeight="1">
@@ -10865,7 +10866,7 @@
         <v>281</v>
       </c>
       <c r="E118" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15.75" customHeight="1">
@@ -10882,7 +10883,7 @@
         <v>282</v>
       </c>
       <c r="E119" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15.75" customHeight="1">
@@ -10896,180 +10897,180 @@
         <v>288</v>
       </c>
       <c r="D120" s="27" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="E120" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15.75" customHeight="1">
       <c r="A121" s="27" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B121" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C121" s="39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E121" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15.75" customHeight="1">
       <c r="A122" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B122" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C122" s="39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D122" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15.75" customHeight="1">
       <c r="A123" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B123" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C123" s="39" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D123" s="22" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15.75" customHeight="1">
       <c r="A124" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B124" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E124" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15.75" customHeight="1">
       <c r="A125" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B125" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D125" s="22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E125" s="27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15.75" customHeight="1">
       <c r="A126" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B126" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E126" s="27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15.75" customHeight="1">
       <c r="A127" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B127" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C127" s="39" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E127" s="27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.75" customHeight="1">
       <c r="A128" s="27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B128" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C128" s="39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E128" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15.75" customHeight="1">
       <c r="A129" s="27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B129" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C129" s="39" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D129" s="22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E129" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15.75" customHeight="1">
       <c r="A130" s="27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B130" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C130" s="39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E130" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4D0BAE-1568-4823-9E0A-3A69A7C37A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_NormalDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4D0BAE-1568-4823-9E0A-3A69A7C37A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C403CD1A-8A72-49FA-AF74-D3143D2D2C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_NomalDialogue" sheetId="1" r:id="rId1"/>
@@ -312,10 +312,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>얼마 전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함꼐 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>character_Hyunwoo_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -8153,6 +8149,10 @@
   </si>
   <si>
     <t>mindDialogue_Ending_1_1_13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼마 전 데이트에서도 전만큼 재미있지 않다고 느꼈고, 오늘도 너와 함께 게임하면서 사소한 다툼이 있었잖아? 근데 평소였으면 엄청 서운하고, 속상해서 너한테 분명하게 말했을거야.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -8738,7 +8738,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
@@ -8764,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F3" s="36" t="s">
         <v>2</v>
@@ -8790,7 +8790,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="38"/>
@@ -8810,7 +8810,7 @@
         <v>23</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F5" s="22"/>
       <c r="G5" s="38"/>
@@ -8830,7 +8830,7 @@
         <v>24</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F6" s="22"/>
       <c r="G6" s="38"/>
@@ -8850,7 +8850,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F7" s="38"/>
       <c r="G7" s="38"/>
@@ -8870,7 +8870,7 @@
         <v>73</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
@@ -8890,7 +8890,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -8910,7 +8910,7 @@
         <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -8930,7 +8930,7 @@
         <v>37</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -8950,7 +8950,7 @@
         <v>38</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -8970,7 +8970,7 @@
         <v>39</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -8984,13 +8984,13 @@
         <v>21</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>76</v>
+        <v>318</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -9010,7 +9010,7 @@
         <v>41</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -9030,7 +9030,7 @@
         <v>42</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -9050,7 +9050,7 @@
         <v>46</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -9070,7 +9070,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -9090,7 +9090,7 @@
         <v>48</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -9110,7 +9110,7 @@
         <v>49</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -9130,7 +9130,7 @@
         <v>53</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -9150,7 +9150,7 @@
         <v>55</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -9170,7 +9170,7 @@
         <v>57</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -9190,7 +9190,7 @@
         <v>58</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -9210,7 +9210,7 @@
         <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -9230,7 +9230,7 @@
         <v>64</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -9250,7 +9250,7 @@
         <v>65</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -9270,7 +9270,7 @@
         <v>66</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -9290,7 +9290,7 @@
         <v>69</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -9310,7 +9310,7 @@
         <v>70</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
@@ -9330,7 +9330,7 @@
         <v>71</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -9338,19 +9338,19 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>79</v>
-      </c>
       <c r="D32" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -9358,19 +9358,19 @@
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -9378,19 +9378,19 @@
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -9398,19 +9398,19 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>85</v>
-      </c>
       <c r="D35" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
@@ -9418,19 +9418,19 @@
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
       <c r="A36" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="D36" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
@@ -9438,19 +9438,19 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
@@ -9458,19 +9458,19 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
       <c r="A38" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -9478,19 +9478,19 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
@@ -9498,19 +9498,19 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="A40" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
@@ -9518,19 +9518,19 @@
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
       <c r="A41" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D41" s="15" t="s">
-        <v>100</v>
-      </c>
       <c r="E41" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -9538,19 +9538,19 @@
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
       <c r="A42" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -9558,19 +9558,19 @@
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1">
       <c r="A43" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
@@ -9578,19 +9578,19 @@
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1">
       <c r="A44" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -9598,19 +9598,19 @@
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
       <c r="A45" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -9618,19 +9618,19 @@
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
       <c r="A46" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
@@ -9638,19 +9638,19 @@
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
       <c r="A47" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B47" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
@@ -9658,19 +9658,19 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
       <c r="A48" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B48" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
@@ -9678,19 +9678,19 @@
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
       <c r="A49" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
@@ -9698,1379 +9698,1379 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1">
       <c r="A50" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1">
       <c r="A51" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B51" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1">
       <c r="A52" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B52" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1">
       <c r="A53" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B53" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B54" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1">
       <c r="A55" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B55" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1">
       <c r="A56" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B56" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15.75" customHeight="1">
       <c r="A58" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B58" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C58" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" customHeight="1">
       <c r="A59" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15.75" customHeight="1">
       <c r="A60" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1">
       <c r="A61" s="27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B61" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1">
       <c r="A62" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B62" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75" customHeight="1">
       <c r="A63" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B63" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75" customHeight="1">
       <c r="A64" s="27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B64" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" customHeight="1">
       <c r="A65" s="27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B65" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" customHeight="1">
       <c r="A66" s="27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B66" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" customHeight="1">
       <c r="A67" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B67" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" customHeight="1">
       <c r="A68" s="27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B68" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" customHeight="1">
       <c r="A69" s="27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B69" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" customHeight="1">
       <c r="A70" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B70" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E70" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" customHeight="1">
       <c r="A71" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B71" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" customHeight="1">
       <c r="A72" s="27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B72" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" customHeight="1">
       <c r="A73" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B73" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E73" s="27" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" customHeight="1">
       <c r="A74" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B74" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" customHeight="1">
       <c r="A75" s="27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B75" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" customHeight="1">
       <c r="A76" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B76" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D76" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" customHeight="1">
       <c r="A77" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B77" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E77" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.75" customHeight="1">
       <c r="A78" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B78" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E78" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15.75" customHeight="1">
       <c r="A79" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B79" s="31" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15.75" customHeight="1">
       <c r="A80" s="27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B80" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15.75" customHeight="1">
       <c r="A81" s="27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B81" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15.75" customHeight="1">
       <c r="A82" s="27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B82" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E82" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15.75" customHeight="1">
       <c r="A83" s="27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B83" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15.75" customHeight="1">
       <c r="A84" s="27" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B84" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E84" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15.75" customHeight="1">
       <c r="A85" s="27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B85" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15.75" customHeight="1">
       <c r="A86" s="27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B86" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E86" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" customHeight="1">
       <c r="A87" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B87" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15.75" customHeight="1">
       <c r="A88" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B88" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E88" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15.75" customHeight="1">
       <c r="A89" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B89" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="15.75" customHeight="1">
       <c r="A90" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B90" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E90" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="15.75" customHeight="1">
       <c r="A91" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B91" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E91" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15.75" customHeight="1">
       <c r="A92" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B92" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E92" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="15.75" customHeight="1">
       <c r="A93" s="27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B93" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E93" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="15.75" customHeight="1">
       <c r="A94" s="27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B94" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E94" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="15.75" customHeight="1">
       <c r="A95" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B95" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E95" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="15.75" customHeight="1">
       <c r="A96" s="27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B96" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E96" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15.75" customHeight="1">
       <c r="A97" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B97" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E97" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="15.75" customHeight="1">
       <c r="A98" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B98" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E98" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="15.75" customHeight="1">
       <c r="A99" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B99" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E99" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="15.75" customHeight="1">
       <c r="A100" s="27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B100" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C100" s="27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E100" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="15.75" customHeight="1">
       <c r="A101" s="27" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B101" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E101" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="15.75" customHeight="1">
       <c r="A102" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="B102" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C102" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="C102" s="27" t="s">
+      <c r="D102" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="D102" s="27" t="s">
-        <v>243</v>
-      </c>
       <c r="E102" s="22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="15.75" customHeight="1">
       <c r="A103" s="27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B103" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C103" s="39" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D103" s="27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E103" s="22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="15.75" customHeight="1">
       <c r="A104" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="B104" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="C104" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="D104" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="B104" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="C104" s="39" t="s">
+      <c r="E104" s="27" t="s">
         <v>245</v>
-      </c>
-      <c r="D104" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="E104" s="27" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="15.75" customHeight="1">
       <c r="A105" s="27" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B105" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C105" s="39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D105" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E105" s="27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="15.75" customHeight="1">
       <c r="A106" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C106" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="D106" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="B106" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="C106" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="D106" s="27" t="s">
+      <c r="E106" s="27" t="s">
         <v>254</v>
-      </c>
-      <c r="E106" s="27" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="15.75" customHeight="1">
       <c r="A107" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="B107" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C107" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="D107" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="B107" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="C107" s="39" t="s">
-        <v>250</v>
-      </c>
-      <c r="D107" s="27" t="s">
-        <v>258</v>
-      </c>
       <c r="E107" s="41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="15.75" customHeight="1">
       <c r="A108" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="B108" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="C108" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="D108" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="B108" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="C108" s="39" t="s">
-        <v>256</v>
-      </c>
-      <c r="D108" s="27" t="s">
-        <v>260</v>
-      </c>
       <c r="E108" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.75" customHeight="1">
       <c r="A109" s="27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B109" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C109" s="39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D109" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="E109" s="27" t="s">
         <v>264</v>
-      </c>
-      <c r="E109" s="27" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="15.75" customHeight="1">
       <c r="A110" s="40" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D110" s="27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E110" s="22" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="15.75" customHeight="1">
       <c r="A111" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B111" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C111" s="27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D111" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E111" s="27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="15.75" customHeight="1">
       <c r="A112" s="40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B112" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D112" s="27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="15.75" customHeight="1">
       <c r="A113" s="27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B113" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D113" s="27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15.75" customHeight="1">
       <c r="A114" s="27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B114" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E114" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="15.75" customHeight="1">
       <c r="A115" s="40" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B115" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C115" s="39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E115" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15.75" customHeight="1">
       <c r="A116" s="27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B116" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C116" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D116" s="27" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E116" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15.75" customHeight="1">
       <c r="A117" s="27" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B117" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D117" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E117" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15.75" customHeight="1">
       <c r="A118" s="40" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B118" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C118" s="39" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D118" s="27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E118" s="27" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15.75" customHeight="1">
       <c r="A119" s="27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B119" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C119" s="39" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D119" s="27" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E119" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15.75" customHeight="1">
       <c r="A120" s="40" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B120" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C120" s="39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D120" s="27" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E120" s="27" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15.75" customHeight="1">
       <c r="A121" s="27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B121" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C121" s="39" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E121" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15.75" customHeight="1">
       <c r="A122" s="27" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B122" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C122" s="39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D122" s="27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15.75" customHeight="1">
       <c r="A123" s="27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B123" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C123" s="39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D123" s="22" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15.75" customHeight="1">
       <c r="A124" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B124" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E124" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15.75" customHeight="1">
       <c r="A125" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B125" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D125" s="22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E125" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15.75" customHeight="1">
       <c r="A126" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B126" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E126" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15.75" customHeight="1">
       <c r="A127" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B127" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C127" s="39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E127" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.75" customHeight="1">
       <c r="A128" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B128" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C128" s="39" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E128" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15.75" customHeight="1">
       <c r="A129" s="27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B129" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C129" s="39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D129" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E129" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15.75" customHeight="1">
       <c r="A130" s="27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B130" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C130" s="39" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E130" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15.75" customHeight="1">
